--- a/week3/manual_gold/920116_星图测控_gold.xlsx
+++ b/week3/manual_gold/920116_星图测控_gold.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>数据来源类型</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -502,6 +512,11 @@
           <t>2016年12月，四方股份出资1200万元（对应持有星图测控有限60%股权）</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +559,11 @@
           <t>罗永红出资400万元（对应持有星图测控有限20%股权，为牛威代持）</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -586,6 +606,11 @@
           <t>王金林出资400万元（对应持有星图测控有限20%股权，为吴功友代持）</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -628,6 +653,11 @@
           <t>2020年9月，中科星图以货币651万元认缴新增注册资本434万元</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -670,6 +700,11 @@
           <t>2022年11月股改，净资产8131.50万元按1.0842:1折为7500万股</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -712,6 +747,11 @@
           <t>2023年5月定向发行，策星银河认购279万股，每股6.30元</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -754,6 +794,11 @@
           <t>策星逐日认购171万股</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -794,6 +839,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>幸福二期认购300万股</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>直接披露</t>
         </is>
       </c>
     </row>
@@ -808,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,6 +912,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>时点说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -914,6 +969,11 @@
           <t>四方股份出资1200万元，持有60%股权</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -966,6 +1026,11 @@
           <t>罗永红出资400万元（代牛威）</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1018,6 +1083,11 @@
           <t>王金林出资400万元（代吴功友）</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1070,6 +1140,7 @@
           <t>代持还原后四方股份仍持股60%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1122,6 +1193,7 @@
           <t>罗永红将所持20%股权转让给牛威</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1174,6 +1246,7 @@
           <t>王金林将所持20%股权转让给吴功友</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1226,6 +1299,11 @@
           <t>2020年9月增资后注册资本增至2434万元</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1278,6 +1356,11 @@
           <t>发行前中科星图持股46.36%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1330,6 +1413,11 @@
           <t>策星九天持股28.43%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1382,6 +1470,11 @@
           <t>幸福一期持股11.12%</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1432,6 +1525,11 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>策星揽月持股5.00%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,6 +1721,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>转让类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1665,6 +1768,11 @@
           <t>罗永红将其持有的星图测控有限20%股权转让予牛威，系还原股权代持，未实际支付股权转让对价</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1705,6 +1813,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>王金林将其持有的星图测控有限20%股权转让予吴功友，系还原股权代持，未实际支付股权转让对价</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
         </is>
       </c>
     </row>
